--- a/output/pdf_financials_xlsx/GKO.xlsx
+++ b/output/pdf_financials_xlsx/GKO.xlsx
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000325</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>-0.122894</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.057816</v>
+        <v>-0.058141</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>-0.122894</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.057816</v>
+        <v>-0.058141</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.069136</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.029186</v>
       </c>
     </row>
     <row r="35">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.069136</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.029186</v>
       </c>
     </row>
     <row r="37">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">

--- a/output/pdf_financials_xlsx/GKO.xlsx
+++ b/output/pdf_financials_xlsx/GKO.xlsx
@@ -521,15 +521,11 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
@@ -560,20 +556,14 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -599,15 +589,11 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
@@ -638,20 +624,14 @@
       <c r="D7" s="3" t="n">
         <v>0.004646</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -677,20 +657,14 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
@@ -716,20 +690,14 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0</v>
@@ -755,20 +723,14 @@
       <c r="D10" s="3" t="n">
         <v>0.058141</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.06474199999999999</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.039962</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>3.835243</v>
@@ -794,15 +756,11 @@
       <c r="D11" s="3" t="n">
         <v>-0.058141</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.06474199999999999</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -833,20 +791,14 @@
       <c r="D12" s="3" t="n">
         <v>0.000325</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -872,20 +824,14 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>-0</v>
@@ -911,20 +857,14 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
@@ -950,20 +890,14 @@
       <c r="D15" s="3" t="n">
         <v>0.001178</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>9.899999999999999e-05</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.000281</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.000202</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0</v>
@@ -989,15 +923,11 @@
       <c r="D16" s="3" t="n">
         <v>-0.057816</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.06474199999999999</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1028,20 +958,14 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1161,15 +1085,11 @@
       <c r="D20" s="3" t="n">
         <v>-0.057816</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-0.06474199999999999</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1200,20 +1120,14 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -1239,20 +1153,14 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -1313,20 +1221,14 @@
       <c r="D24" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.004</v>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
@@ -1356,20 +1258,14 @@
       <c r="D25" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.004</v>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
@@ -1401,10 +1297,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="3" t="n">
+        <v>7.41</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1444,15 +1338,11 @@
       <c r="D27" s="3" t="n">
         <v>-0.058141</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-0.06474199999999999</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1483,20 +1373,14 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.449626</v>
@@ -1522,15 +1406,11 @@
       <c r="D29" s="3" t="n">
         <v>-0.058141</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-0.06474199999999999</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1608,15 +1488,11 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -1699,20 +1575,14 @@
       <c r="D34" s="3" t="n">
         <v>0.115814</v>
       </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" s="3" t="n">
+        <v>0.110541</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.023079</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.009032999999999999</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.069136</v>
@@ -1741,15 +1611,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0</v>
@@ -1773,20 +1639,14 @@
       <c r="D36" s="3" t="n">
         <v>0.115814</v>
       </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E36" s="3" t="n">
+        <v>0.110541</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.023079</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.009032999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.069136</v>
@@ -1815,15 +1675,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.06572699999999999</v>
@@ -1852,15 +1708,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
@@ -1889,15 +1741,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0</v>
@@ -1926,15 +1774,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -1963,15 +1807,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.06572699999999999</v>
@@ -2000,15 +1840,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0</v>
@@ -2037,15 +1873,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0</v>
@@ -2074,15 +1906,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0</v>
@@ -2111,15 +1939,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0</v>
@@ -2148,15 +1972,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0</v>
@@ -2185,15 +2005,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0</v>
@@ -2222,15 +2038,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F48" s="3" t="n">
+        <v>0.025121</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.026912</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -2259,15 +2071,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" s="3" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.035945</v>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
@@ -2300,15 +2108,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
@@ -2337,15 +2141,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0</v>
@@ -2374,15 +2174,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0</v>
@@ -2411,15 +2207,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -2448,15 +2240,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0</v>
@@ -2532,15 +2320,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0</v>
@@ -2569,15 +2353,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0</v>
@@ -2606,15 +2386,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.004272</v>
@@ -2643,15 +2419,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.654687</v>
@@ -2680,15 +2452,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0</v>
@@ -2717,15 +2485,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0</v>
@@ -2844,15 +2608,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>1.087253</v>
@@ -2881,15 +2641,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0</v>
@@ -2918,15 +2674,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0</v>
@@ -2955,15 +2707,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -2987,20 +2735,14 @@
       <c r="D68" s="3" t="n">
         <v>0.027951</v>
       </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="3" t="n">
+        <v>0.077061</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.020973</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.04868</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>1.087253</v>
@@ -3029,15 +2771,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0</v>
@@ -3066,15 +2804,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
@@ -3103,15 +2837,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0</v>
@@ -3140,15 +2870,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0</v>
@@ -3177,15 +2903,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0</v>
@@ -3214,15 +2936,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0</v>
@@ -3251,15 +2969,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>1.685389</v>
@@ -3331,15 +3045,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0</v>
@@ -3368,15 +3078,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0</v>
@@ -3405,15 +3111,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0</v>
@@ -3489,15 +3191,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0</v>
@@ -3526,15 +3224,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0</v>
@@ -3563,15 +3257,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0</v>
@@ -3600,15 +3290,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0</v>
@@ -3637,15 +3323,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>3.133898</v>
@@ -3755,20 +3437,14 @@
       <c r="D88" s="3" t="n">
         <v>0.19789</v>
       </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="3" t="n">
+        <v>0.517637</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.517637</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.517637</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>7.024028</v>
@@ -3797,15 +3473,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0</v>
@@ -3873,15 +3545,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0</v>
@@ -3905,20 +3573,14 @@
       <c r="D92" s="3" t="n">
         <v>0.074824</v>
       </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="3" t="n">
+        <v>0.074824</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.074824</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.074824</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>3.393882</v>
@@ -3947,15 +3609,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>0</v>
@@ -4021,15 +3679,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H95" s="3" t="n">
         <v>0</v>
@@ -5535,7 +5189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6786,7 +6440,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CURRENT ASSETS</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6799,29 +6453,29 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.163287</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.115814</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.110541</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.023079</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.009032999999999999</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -6842,7 +6496,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CURRENT ASSETS</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6856,26 +6510,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>0.008095</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.002512</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.033489</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0.025121</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0.026912</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -6896,17 +6548,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CURRENT ASSETS</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Interest receivable</t>
+          <t>Current assets total</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6919,23 +6571,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>0.000325</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="5" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0.035945</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -6956,17 +6606,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CURRENT ASSETS</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Accounts payable and accrued liabilities $</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6979,23 +6629,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n">
-        <v>0.001304</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.077061</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0.020973</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0.04868</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -7016,42 +6662,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CURRENT ASSETS</t>
+          <t>Shareholders’ equity (deficiency)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CURRENT ASSETS total</t>
+          <t>Share capital (Note 5)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>0.171382</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.119955</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="5" t="n">
+        <v>0.517637</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.517637</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -7072,17 +6720,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CURRENT LIABILITIES</t>
+          <t>Shareholders’ equity (deficiency)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accrued liabilities $</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CurrentAccruedExpenses</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -7090,26 +6738,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>0.021562</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.027951</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="5" t="n">
+        <v>0.074824</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0.074824</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -7130,42 +6778,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>( 12,735 )        27,227</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CAPITAL STOCK (note 8)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.19789</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.19789</v>
+          <t>( 12,735 )        27,227</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="5" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0.035945</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -7186,39 +6832,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CONTRIBUTED SURPLUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>Deposit paid for Qualifying Transaction (Note 4)          −             25,000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>0.074824</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.074824</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.16903</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0.0482</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -7244,17 +6886,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DEFICIT</t>
+          <t>Share capital (Note 5)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7262,21 +6904,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>-0.122894</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>-0.18071</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.517637</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.517637</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -7302,17 +6944,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>shares     Capital stock      surplus           Deficit           equity</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>shares     Capital stock      surplus           Deficit           equity</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>0.1</v>
+          <t>Contributed surplus</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -7324,15 +6972,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H32" s="5" t="n">
+        <v>0.074824</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.074824</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -7358,17 +7002,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Private placement</t>
+          <t>Deficit                                                         (565,234 )      (500,492)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Private placement issued in cash 700,000 35,000</t>
+          <t>Deficit                                                         (565,234 )      (500,492) total</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>0.035</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -7380,15 +7026,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>0.091969</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.027227</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -7414,17 +7056,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Public offering issued in</t>
+          <t>Deficit                                                         (565,234 )      (500,492)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Public offering issued in cash 2,000,000 200,000</t>
+          <t>Deficit                                                         (565,234 )      (500,492)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>0.2</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -7436,15 +7080,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H34" s="5" t="n">
+        <v>0.16903</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0.0482</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -7470,27 +7110,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public offering issued in</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Share issue expenses - (118,470)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Cash and cash equivalents $</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>-0.11847</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.163287</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.115814</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -7526,12 +7166,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Public offering issued in</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Agent’s option - (18,640)</t>
+          <t>Sales taxes recoverable</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -7540,13 +7180,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" s="5" t="n">
+        <v>0.008095</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.01864</v>
+        <v>0.002512</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -7582,17 +7220,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stock-based</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stock-based compensation - -</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>0.056184</v>
+          <t>Interest receivable</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -7600,7 +7244,7 @@
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.056184</v>
+        <v>0.000325</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -7636,25 +7280,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stock-based</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net loss - -</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="n">
-        <v>-0.122894</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>-0.122894</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.001304</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -7690,23 +7340,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stock-based</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stock-based total</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>CURRENT ASSETS total</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>0.14982</v>
+        <v>0.1</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-0.122894</v>
+        <v>0.171382</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.074824</v>
+        <v>0.119955</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -7737,22 +7391,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>CURRENT LIABILITIES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Accrued liabilities $</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>CurrentAccruedExpenses</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -7760,15 +7414,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F40" s="5" t="n">
+        <v>0.021562</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.027951</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -7785,44 +7435,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K40" s="5" t="n">
-        <v>-3.835243</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>-1.953726</v>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Change in the fair value of a financial asset</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CAPITAL STOCK (note 8)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.19789</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.19789</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -7839,44 +7491,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K41" s="5" t="n">
-        <v>0.8187449999999999</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>-1.285037</v>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deferred Income Taxes                                  (137,903)</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Financial Expenses</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>CONTRIBUTED SURPLUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F42" s="5" t="n">
+        <v>0.074824</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.074824</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -7893,32 +7549,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="5" t="n">
-        <v>0.757698</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0.378157</v>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deferred Income Taxes                                  (137,903)</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Amortization and depreciation</t>
+          <t>DEFICIT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7926,15 +7586,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="5" t="n">
+        <v>-0.122894</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.18071</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -7951,38 +7607,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K43" s="5" t="n">
-        <v>0.449626</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>0.466619</v>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deferred Income Taxes                                  (137,903)</t>
+          <t>shares     Capital stock      surplus           Deficit           equity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>shares     Capital stock      surplus           Deficit           equity</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
+        <v>0.1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -8009,34 +7663,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K44" s="5" t="n">
-        <v>0.112733</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0.114027</v>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>related to royalties                                       (314,060)</t>
+          <t>Private placement</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Impairment Loss</t>
+          <t>Private placement issued in cash 700,000 35,000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="5" t="n">
+        <v>0.035</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -8063,34 +7719,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K45" s="5" t="n">
-        <v>1.142034</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>1.9766</v>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>related to royalties                                       (314,060)</t>
+          <t>Public offering issued in</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>related to royalties                                       (314,060) total</t>
+          <t>Public offering issued in cash 2,000,000 200,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -8117,34 +7775,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K46" s="5" t="n">
-        <v>-0.554407</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>-0.755323</v>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net change in working capital items</t>
+          <t>Public offering issued in</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>(note 15)</t>
+          <t>Share issue expenses - (118,470)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="5" t="n">
+        <v>-0.11847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -8171,34 +7831,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K47" s="5" t="n">
-        <v>0.164526</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>0.045866</v>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Net change in working capital items</t>
+          <t>Public offering issued in</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Agent’s option - (18,640)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -8209,10 +7869,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="5" t="n">
+        <v>0.01864</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -8229,44 +7887,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K48" s="5" t="n">
-        <v>-0.389881</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>-0.709457</v>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Stock-based</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Stock-based compensation - -</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="5" t="n">
+        <v>0.056184</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G49" s="5" t="n">
+        <v>0.056184</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -8283,43 +7941,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K49" s="5" t="n">
-        <v>-0.119266</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>-0.06296300000000001</v>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Stock-based</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss - -</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" s="5" t="n">
+        <v>-0.122894</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>-0.122894</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -8341,48 +7995,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K50" s="5" t="n">
-        <v>-0.119266</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>-0.06296300000000001</v>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Promissory note                                                60,000</t>
+          <t>Stock-based</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Issuance of shares</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock-based total</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" s="5" t="n">
+        <v>0.14982</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-0.122894</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.074824</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -8399,11 +8047,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K51" s="5" t="n">
-        <v>0.94755</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>0.67247</v>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -8414,17 +8066,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Promissory note                                                60,000</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8458,10 +8110,10 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0.53855</v>
+        <v>-3.835243</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.73247</v>
+        <v>-1.953726</v>
       </c>
     </row>
     <row r="53">
@@ -8472,19 +8124,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Promissory note                                                60,000</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Change in the fair value of a financial asset</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -8516,10 +8164,10 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.029403</v>
+        <v>0.8187449999999999</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.03995</v>
+        <v>-1.285037</v>
       </c>
     </row>
     <row r="54">
@@ -8530,19 +8178,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Promissory note                                                60,000</t>
+          <t>Deferred Income Taxes                                  (137,903)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Financial Expenses</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -8574,10 +8218,10 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0.039733</v>
+        <v>0.757698</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.069136</v>
+        <v>0.378157</v>
       </c>
     </row>
     <row r="55">
@@ -8588,17 +8232,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Promissory note                                                60,000</t>
+          <t>Deferred Income Taxes                                  (137,903)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Amortization and depreciation</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -8632,10 +8276,10 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.069136</v>
+        <v>0.449626</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.029186</v>
+        <v>0.466619</v>
       </c>
     </row>
     <row r="56">
@@ -8646,15 +8290,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1 - GOVERNING STATUTES</t>
+          <t>Deferred Income Taxes                                  (137,903)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IFRS Accounting standards as issued by the International Accounting Standards Board (IASB) issuance by the Board of Directors on April</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -8686,10 +8334,10 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.002026</v>
+        <v>0.112733</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.114027</v>
       </c>
     </row>
     <row r="57">
@@ -8700,12 +8348,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3 - GOING CONCERN ASSUMPTION</t>
+          <t>related to royalties                                       (314,060)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Company has a $ 1,953,726 net loss for the year ended December</t>
+          <t>Impairment Loss</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -8740,10 +8388,10 @@
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0.002025</v>
+        <v>1.142034</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>1.9766</v>
       </c>
     </row>
     <row r="58">
@@ -8754,12 +8402,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3 - GOING CONCERN ASSUMPTION</t>
+          <t>related to royalties                                       (314,060)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(December 31, 2024 - loss of $ 3,835,243 ) and an accumulated deficit of $ 14,120,937 as at December</t>
+          <t>related to royalties                                       (314,060) total</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -8794,10 +8442,10 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.002025</v>
+        <v>-0.554407</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.755323</v>
       </c>
     </row>
     <row r="59">
@@ -8808,19 +8456,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>( 14,046 )              ( 87,462 )</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>(note 15)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -8841,21 +8485,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>0.110541</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>0.023079</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.164526</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.045866</v>
       </c>
     </row>
     <row r="60">
@@ -8866,17 +8510,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>( 14,046 )              ( 87,462 )</t>
+          <t>Net change in working capital items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8899,21 +8543,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>0.023079</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>0.009032999999999999</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>-0.389881</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>-0.709457</v>
       </c>
     </row>
     <row r="61">
@@ -8924,19 +8568,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -8952,26 +8592,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H61" s="5" t="n">
-        <v>-0.1482</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>-0.06474199999999999</v>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K61" s="5" t="n">
+        <v>-0.119266</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>-0.06296300000000001</v>
       </c>
     </row>
     <row r="62">
@@ -8982,15 +8622,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Non-cash item</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Non-cash item total</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -9006,26 +8650,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H62" s="5" t="n">
-        <v>-0.1482</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>-0.039742</v>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K62" s="5" t="n">
+        <v>-0.119266</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>-0.06296300000000001</v>
       </c>
     </row>
     <row r="63">
@@ -9036,15 +8680,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Non-cash item</t>
+          <t>Promissory note                                                60,000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Issuance of shares</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -9060,26 +8708,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="5" t="n">
-        <v>0.018259</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>-0.04772</v>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K63" s="5" t="n">
+        <v>0.94755</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>0.67247</v>
       </c>
     </row>
     <row r="64">
@@ -9090,17 +8738,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Promissory note                                                60,000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash and cash equivalents</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -9118,26 +8766,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="5" t="n">
-        <v>0.07002899999999999</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>-0.087462</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K64" s="5" t="n">
+        <v>0.53855</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0.73247</v>
       </c>
     </row>
     <row r="65">
@@ -9148,17 +8796,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Promissory note                                                60,000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Net increase (decrease) in cash</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -9176,26 +8824,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n">
-        <v>0.040512</v>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>0.110541</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K65" s="5" t="n">
+        <v>0.029403</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-0.03995</v>
       </c>
     </row>
     <row r="66">
@@ -9206,17 +8854,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Promissory note                                                60,000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -9234,26 +8882,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" s="5" t="n">
-        <v>0.110541</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>0.023079</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K66" s="5" t="n">
+        <v>0.039733</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0.069136</v>
       </c>
     </row>
     <row r="67">
@@ -9264,15 +8912,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>or businesses (“Transaction”).</t>
+          <t>Promissory note                                                60,000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>The financial statements were approved by the Board of Directors on May</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -9288,49 +8940,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>2.8e-05</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K67" s="5" t="n">
+        <v>0.069136</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>0.029186</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>1 - GOVERNING STATUTES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Selling expenses</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SellingExpense</t>
-        </is>
-      </c>
+          <t>IFRS Accounting standards as issued by the International Accounting Standards Board (IASB) issuance by the Board of Directors on April</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -9362,33 +9010,29 @@
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>0.0401</v>
+        <v>0.002026</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.045</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>3 - GOING CONCERN ASSUMPTION</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>The Company has a $ 1,953,726 net loss for the year ended December</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -9420,33 +9064,29 @@
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>0.62704</v>
+        <v>0.002025</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.824349</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>3 - GOING CONCERN ASSUMPTION</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Amortization and depreciation</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>(December 31, 2024 - loss of $ 3,835,243 ) and an accumulated deficit of $ 14,120,937 as at December</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -9478,29 +9118,33 @@
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>0.449626</v>
+        <v>0.002025</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>0.466619</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>( 14,046 )              ( 87,462 )</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Financial expenses</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -9521,40 +9165,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>0.757698</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>0.378157</v>
+      <c r="I71" s="5" t="n">
+        <v>0.110541</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>0.023079</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>( 14,046 )              ( 87,462 )</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>(Note</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -9575,40 +9223,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>-0.31406</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>2.02e-05</v>
+      <c r="I72" s="5" t="n">
+        <v>0.023079</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0.009032999999999999</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Impairment Loss</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -9624,42 +9276,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-0.06474199999999999</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K73" s="5" t="n">
-        <v>1.142034</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>1.9766</v>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-cash item</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Change in fair value of a financial asset</t>
+          <t>Non-cash item total</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -9678,49 +9330,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-0.039742</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K74" s="5" t="n">
-        <v>0.8187449999999999</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>-1.285037</v>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-cash item</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Net change in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -9736,47 +9384,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>0.018259</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>-0.04772</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K75" s="5" t="n">
-        <v>3.835243</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>2.091629</v>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Increase (decrease) in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -9794,45 +9442,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H76" s="5" t="n">
+        <v>0.07002899999999999</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>-0.087462</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>-3.835243</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>-2.091629</v>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Deferred Income Tax (Note</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -9848,47 +9500,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H77" s="5" t="n">
+        <v>0.040512</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0.110541</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K77" s="5" t="n">
-        <v>0.137903</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>1.3e-05</v>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive income</t>
+          <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9906,42 +9558,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>0.110541</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0.023079</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K78" s="5" t="n">
-        <v>-3.835243</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-1.953726</v>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Basic and diluted earnings per share</t>
+          <t>or businesses (“Transaction”).</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>(Note 14)</t>
+          <t>The financial statements were approved by the Board of Directors on May</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -9960,26 +9612,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H79" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>2.8e-05</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K79" s="5" t="n">
-        <v>-6.4e-08</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>-2.5e-08</v>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -9988,15 +9640,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>INTEREST INCOME $</t>
+          <t>Selling expenses</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingExpense</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -10009,8 +9665,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="5" t="n">
-        <v>0.000325</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -10027,15 +9685,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K80" s="5" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>0.045</v>
       </c>
     </row>
     <row r="81">
@@ -10046,22 +9700,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Stock-based compensation to directors</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>0.056184</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -10083,15 +9743,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K81" s="5" t="n">
+        <v>0.62704</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>0.824349</v>
       </c>
     </row>
     <row r="82">
@@ -10102,17 +9758,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Amortization and depreciation</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -10120,11 +9776,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>0.04278</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>0.032994</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -10141,15 +9801,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K82" s="5" t="n">
+        <v>0.449626</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0.466619</v>
       </c>
     </row>
     <row r="83">
@@ -10160,12 +9816,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Regulatory expenses</t>
+          <t>Financial expenses</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -10174,11 +9830,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>0.01575</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.019323</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -10195,15 +9855,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K83" s="5" t="n">
+        <v>0.757698</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>0.378157</v>
       </c>
     </row>
     <row r="84">
@@ -10214,19 +9870,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>(Note</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -10237,8 +9889,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G84" s="5" t="n">
-        <v>0.004646</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -10255,15 +9909,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K84" s="5" t="n">
+        <v>-0.31406</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>2.02e-05</v>
       </c>
     </row>
     <row r="85">
@@ -10274,29 +9924,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Impairment Loss</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>0.00818</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.001178</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -10313,15 +9963,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K85" s="5" t="n">
+        <v>1.142034</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>1.9766</v>
       </c>
     </row>
     <row r="86">
@@ -10332,29 +9978,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Change in fair value of a financial asset</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>0.122894</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>0.058141</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -10371,15 +10017,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K86" s="5" t="n">
+        <v>0.8187449999999999</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-1.285037</v>
       </c>
     </row>
     <row r="87">
@@ -10390,50 +10032,48 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TAXES</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>-0.122894</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>-0.057816</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.06474199999999999</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.039962</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>3.835243</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>2.091629</v>
       </c>
     </row>
     <row r="88">
@@ -10444,17 +10084,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>INCOME TAXES (Note 10)</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10487,15 +10127,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K88" s="5" t="n">
+        <v>-3.835243</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>-2.091629</v>
       </c>
     </row>
     <row r="89">
@@ -10506,29 +10142,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NET LOSS AND NET COMPREHENSIVE LOSS $</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred Income Tax (Note</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.122894</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-0.057816</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -10545,15 +10181,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K89" s="5" t="n">
+        <v>0.137903</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>1.3e-05</v>
       </c>
     </row>
     <row r="90">
@@ -10564,17 +10196,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NET LOSS PER SHARE BASIC AND DILUTED $</t>
+          <t>Net loss and comprehensive income</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10582,11 +10214,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -10603,15 +10239,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K90" s="5" t="n">
+        <v>-3.835243</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>-1.953726</v>
       </c>
     </row>
     <row r="91">
@@ -10622,12 +10254,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+          <t>Basic and diluted earnings per share</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF CLASS A SHARES</t>
+          <t>(Note 14)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -10636,33 +10268,1213 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-6.4e-08</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>-2.5e-08</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Regulatory expenses $</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0.011492</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0.010781</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.118805</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0.027969</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0.028979</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>9.899999999999999e-05</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0.000281</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0.000202</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Loss per share basic and diluted</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>-7e-09</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Weighted average number of class A shares</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>6.684932</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Regulatory expenses</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.029296</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.011492</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>-0.1482</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>-0.06474199999999999</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Total Equity 15,199 (148,200) 224,970 91,969</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.027227</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>-0.06474199999999999</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>− (64,742) Deficit (352,292) (148,200)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>-0.565234</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.500492</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>INTEREST INCOME $</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.000325</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Stock-based compensation to directors</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.056184</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.032994</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Regulatory expenses</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.019323</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.004646</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.00818</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.001178</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0.122894</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.058141</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TAXES</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>-0.122894</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>-0.057816</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>INCOME TAXES (Note 10)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NET LOSS AND NET COMPREHENSIVE LOSS $</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>-0.122894</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>-0.057816</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NET LOSS PER SHARE BASIC AND DILUTED $</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS BEFORE INCOME</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF CLASS A SHARES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
         <v>3.089444</v>
       </c>
-      <c r="G91" s="5" t="n">
+      <c r="G112" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
